--- a/05-rockledge-benefits-ai-governance/artifacts/ai_risk_assessment.xlsx
+++ b/05-rockledge-benefits-ai-governance/artifacts/ai_risk_assessment.xlsx
@@ -529,7 +529,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="35.05" customHeight="1" s="10">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -728,7 +727,7 @@
       </c>
       <c r="U5" s="14" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -823,7 +822,7 @@
       </c>
       <c r="U6" s="14" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -918,7 +917,7 @@
       </c>
       <c r="U7" s="14" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -998,7 +997,7 @@
       </c>
       <c r="R8" s="14" t="inlineStr">
         <is>
-          <t>Obtain written counsel determination on Annex III applicability by 30 Sep 2026 — this is the gating question. Proceed with fairness and explainability work regardless, since it is required on its merits. See Decision Memo for both classification outcomes.</t>
+          <t>Obtain written counsel determination on Annex III applicability by 23 Sep 2026 — this is the gating question. Proceed with fairness and explainability work regardless, since it is required on its merits. See Decision Memo for both classification outcomes.</t>
         </is>
       </c>
       <c r="S8" s="14" t="inlineStr">
@@ -1013,7 +1012,7 @@
       </c>
       <c r="U8" s="14" t="inlineStr">
         <is>
-          <t>2026-09-30 (counsel determination)</t>
+          <t>2026-09-23 (counsel determination)</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1107,7 @@
       </c>
       <c r="U9" s="14" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1202,7 @@
       </c>
       <c r="U10" s="14" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1297,7 @@
       </c>
       <c r="U11" s="14" t="inlineStr">
         <is>
-          <t>2026-08-15 (overdue)</t>
+          <t>2026-08-21 (Art. 50 duty already applied 2026-08-02)</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1392,7 @@
       </c>
       <c r="U12" s="14" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1487,7 @@
       </c>
       <c r="U13" s="14" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1582,7 @@
       </c>
       <c r="U14" s="14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1677,7 @@
       </c>
       <c r="U15" s="14" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-22</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1772,7 @@
       </c>
       <c r="U16" s="14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1867,7 @@
       </c>
       <c r="U17" s="14" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1945,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="23.85" customHeight="1" s="10">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -2150,7 +2148,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="35.05" customHeight="1" s="10">
       <c r="A3" s="15" t="inlineStr">
         <is>

--- a/05-rockledge-benefits-ai-governance/artifacts/ai_risk_assessment.xlsx
+++ b/05-rockledge-benefits-ai-governance/artifacts/ai_risk_assessment.xlsx
@@ -944,7 +944,7 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>If ClaimDesk is High-Risk under Annex III, it operates for 3 EU client plans without conformity assessment, technical documentation, or database registration. Classification is contested: Annex III(5)(a) covers public-authority benefits and (5)(c) covers insurance risk/pricing — neither cleanly covers private claims adjudication.</t>
+          <t>If ClaimDesk is High-Risk under Annex III, it operates for 3 EU client plans without conformity assessment, technical documentation, or database registration. Classification is contested: Annex III(5)(a) covers systems used by or on behalf of public authorities for essential public assistance benefits and (5)(c) covers insurance risk/pricing — neither cleanly covers private claims adjudication.</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>AIR-004 turns on whether ClaimDesk falls within Annex III. It is not clearly enumerated: (5)(a) addresses essential public assistance benefits administered by public authorities, and (5)(c) addresses risk assessment and pricing for life and health insurance. A private administrator adjudicating employer-sponsored benefit claims sits between them. The register treats it as high-risk pending counsel determination, which is the conservative posture, and the Decision Memo presents both outcomes.</t>
+          <t>AIR-004 turns on whether ClaimDesk falls within Annex III. It is not clearly enumerated: (5)(a) addresses systems used by or on behalf of public authorities to evaluate eligibility for essential public assistance benefits, and (5)(c) addresses risk assessment and pricing for life and health insurance. A private administrator adjudicating employer-sponsored benefit claims sits between them; the open question under (5)(a) is whether Rockledge acts on behalf of a public authority. The register treats it as high-risk pending counsel determination, which is the conservative posture, and the Decision Memo presents both outcomes.</t>
         </is>
       </c>
     </row>

--- a/05-rockledge-benefits-ai-governance/artifacts/ai_risk_assessment.xlsx
+++ b/05-rockledge-benefits-ai-governance/artifacts/ai_risk_assessment.xlsx
@@ -529,6 +529,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="35.05" customHeight="1" s="10">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -921,7 +922,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="79.84999999999999" customHeight="1" s="10">
+    <row r="8" ht="104" customHeight="1" s="10">
       <c r="A8" s="14" t="inlineStr">
         <is>
           <t>AIR-004</t>
@@ -1945,6 +1946,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="23.85" customHeight="1" s="10">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -2148,6 +2150,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="35.05" customHeight="1" s="10">
       <c r="A3" s="15" t="inlineStr">
         <is>
@@ -2244,7 +2247,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="46.25" customHeight="1" s="10">
+    <row r="11" ht="64" customHeight="1" s="10">
       <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Contested classification</t>
